--- a/Documents/上料机 IO表-2025-9-15.xlsx
+++ b/Documents/上料机 IO表-2025-9-15.xlsx
@@ -902,7 +902,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -944,7 +944,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -955,12 +955,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -968,9 +962,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1144,13 +1138,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1200,9 +1194,6 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1257,80 +1248,77 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1637,1762 +1625,1762 @@
   <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="61" width="5.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="62" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="39" width="26.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="62" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="61" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="62" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="39" width="37.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="62" width="12.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="58" width="5.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="37" width="26.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="59" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="58" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="59" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="37" width="37.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="59" width="12.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
-      <c r="A1" s="40" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="38" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="40"/>
+      <c r="E1" s="38"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="46">
-      <c r="A5" s="47" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="45">
+      <c r="A5" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="50">
+      <c r="A6" s="49">
         <v>0</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="49">
         <v>0</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="50">
+      <c r="A7" s="49">
         <v>1</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="49">
         <v>1</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="50">
+      <c r="A8" s="49">
         <v>2</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="49">
         <v>2</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="50">
+      <c r="A9" s="49">
         <v>3</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="49">
         <v>3</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="54" t="s">
+      <c r="G9" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="H9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="50">
+      <c r="A10" s="49">
         <v>4</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="49">
         <v>4</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="50">
+      <c r="A11" s="49">
         <v>5</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="49">
         <v>5</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="50">
+      <c r="A12" s="49">
         <v>6</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="49">
         <v>6</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="G12" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="50">
+      <c r="A13" s="49">
         <v>7</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="49">
         <v>7</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="55" t="s">
+      <c r="G13" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="50">
+      <c r="A14" s="49">
         <v>8</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="49">
         <v>8</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="50">
+      <c r="A15" s="49">
         <v>9</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="49">
         <v>9</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="55" t="s">
+      <c r="G15" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="H15" s="51" t="s">
+      <c r="H15" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="50">
+      <c r="A16" s="49">
         <v>10</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="51" t="s">
+      <c r="D16" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="49">
         <v>10</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="55" t="s">
+      <c r="G16" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="H16" s="51" t="s">
+      <c r="H16" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="50">
+      <c r="A17" s="49">
         <v>11</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="49">
         <v>11</v>
       </c>
-      <c r="F17" s="53" t="s">
+      <c r="F17" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="55" t="s">
+      <c r="G17" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="50">
+      <c r="A18" s="49">
         <v>12</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="49">
         <v>12</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="50">
+      <c r="A19" s="49">
         <v>13</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="49">
         <v>13</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="F19" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="51" t="s">
+      <c r="H19" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="50">
+      <c r="A20" s="49">
         <v>14</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="49">
         <v>14</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="56" t="s">
+      <c r="G20" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H20" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="50">
+      <c r="A21" s="49">
         <v>15</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <v>15</v>
       </c>
-      <c r="F21" s="53" t="s">
+      <c r="F21" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="55" t="s">
+      <c r="G21" s="54" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="51" t="s">
+      <c r="H21" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="50">
+      <c r="A22" s="49">
         <v>16</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="51" t="s">
+      <c r="C22" s="54"/>
+      <c r="D22" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="49">
         <v>16</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="56" t="s">
+      <c r="G22" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="H22" s="51" t="s">
+      <c r="H22" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="50">
+      <c r="A23" s="49">
         <v>17</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="49">
         <v>17</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="55" t="s">
+      <c r="G23" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="50">
+      <c r="A24" s="49">
         <v>18</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="51" t="s">
+      <c r="C24" s="53"/>
+      <c r="D24" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="50"/>
-      <c r="F24" s="53"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="52"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="50">
+      <c r="A25" s="49">
         <v>19</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="50"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="50">
+      <c r="A26" s="49">
         <v>20</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="50">
+      <c r="A27" s="49">
         <v>21</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="51" t="s">
+      <c r="C27" s="53"/>
+      <c r="D27" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="50">
+      <c r="A28" s="49">
         <v>22</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="51" t="s">
+      <c r="C28" s="53"/>
+      <c r="D28" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
-      <c r="A29" s="50">
+      <c r="A29" s="49">
         <v>23</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="51" t="s">
+      <c r="C29" s="53"/>
+      <c r="D29" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="50"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
-      <c r="A30" s="50"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5" customFormat="1" s="46">
-      <c r="A34" s="47" t="s">
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5" customFormat="1" s="45">
+      <c r="A34" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="47" t="s">
+      <c r="E34" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="48" t="s">
+      <c r="H34" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
-      <c r="A35" s="50">
+      <c r="A35" s="49">
         <v>24</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="49">
         <v>18</v>
       </c>
-      <c r="F35" s="53" t="s">
+      <c r="F35" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="57" t="s">
+      <c r="G35" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="H35" s="51" t="s">
+      <c r="H35" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="50">
+      <c r="A36" s="49">
         <v>25</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="54" t="s">
+      <c r="C36" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="D36" s="51" t="s">
+      <c r="D36" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="49">
         <v>19</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H36" s="51" t="s">
+      <c r="H36" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
-      <c r="A37" s="50">
+      <c r="A37" s="49">
         <v>26</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="54" t="s">
+      <c r="C37" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="51" t="s">
+      <c r="D37" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="49">
         <v>20</v>
       </c>
-      <c r="F37" s="53" t="s">
+      <c r="F37" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H37" s="51" t="s">
+      <c r="H37" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
-      <c r="A38" s="50">
+      <c r="A38" s="49">
         <v>27</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="54" t="s">
+      <c r="C38" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="51" t="s">
+      <c r="D38" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="E38" s="50">
+      <c r="E38" s="49">
         <v>21</v>
       </c>
-      <c r="F38" s="53" t="s">
+      <c r="F38" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="G38" s="57" t="s">
+      <c r="G38" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H38" s="51" t="s">
+      <c r="H38" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
-      <c r="A39" s="50">
+      <c r="A39" s="49">
         <v>28</v>
       </c>
-      <c r="B39" s="51" t="s">
+      <c r="B39" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="51" t="s">
+      <c r="D39" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="E39" s="50">
+      <c r="E39" s="49">
         <v>22</v>
       </c>
-      <c r="F39" s="53" t="s">
+      <c r="F39" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="G39" s="57" t="s">
+      <c r="G39" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H39" s="51" t="s">
+      <c r="H39" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
-      <c r="A40" s="50">
+      <c r="A40" s="49">
         <v>29</v>
       </c>
-      <c r="B40" s="51" t="s">
+      <c r="B40" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="D40" s="51" t="s">
+      <c r="D40" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="50">
+      <c r="E40" s="49">
         <v>23</v>
       </c>
-      <c r="F40" s="53" t="s">
+      <c r="F40" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="G40" s="57" t="s">
+      <c r="G40" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="H40" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
-      <c r="A41" s="50">
+      <c r="A41" s="49">
         <v>30</v>
       </c>
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="54"/>
-      <c r="D41" s="51" t="s">
+      <c r="C41" s="53"/>
+      <c r="D41" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="E41" s="50">
+      <c r="E41" s="49">
         <v>24</v>
       </c>
-      <c r="F41" s="53" t="s">
+      <c r="F41" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="H41" s="51" t="s">
+      <c r="H41" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
-      <c r="A42" s="50">
+      <c r="A42" s="49">
         <v>31</v>
       </c>
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="54"/>
-      <c r="D42" s="51" t="s">
+      <c r="C42" s="53"/>
+      <c r="D42" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="50">
+      <c r="E42" s="49">
         <v>25</v>
       </c>
-      <c r="F42" s="53" t="s">
+      <c r="F42" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="G42" s="59" t="s">
+      <c r="G42" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="H42" s="51" t="s">
+      <c r="H42" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
-      <c r="A43" s="50">
+      <c r="A43" s="49">
         <v>32</v>
       </c>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="54"/>
-      <c r="D43" s="51" t="s">
+      <c r="C43" s="53"/>
+      <c r="D43" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="E43" s="50">
+      <c r="E43" s="49">
         <v>26</v>
       </c>
-      <c r="F43" s="53" t="s">
+      <c r="F43" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="G43" s="60"/>
-      <c r="H43" s="51" t="s">
+      <c r="G43" s="53"/>
+      <c r="H43" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
-      <c r="A44" s="50">
+      <c r="A44" s="49">
         <v>33</v>
       </c>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="C44" s="54"/>
-      <c r="D44" s="51" t="s">
+      <c r="C44" s="53"/>
+      <c r="D44" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="50">
+      <c r="E44" s="49">
         <v>27</v>
       </c>
-      <c r="F44" s="53" t="s">
+      <c r="F44" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="60"/>
-      <c r="H44" s="51" t="s">
+      <c r="G44" s="53"/>
+      <c r="H44" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
-      <c r="A45" s="50">
+      <c r="A45" s="49">
         <v>34</v>
       </c>
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="54"/>
-      <c r="D45" s="51" t="s">
+      <c r="C45" s="53"/>
+      <c r="D45" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="E45" s="50">
+      <c r="E45" s="49">
         <v>28</v>
       </c>
-      <c r="F45" s="53" t="s">
+      <c r="F45" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="G45" s="54"/>
-      <c r="H45" s="51" t="s">
+      <c r="G45" s="53"/>
+      <c r="H45" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
-      <c r="A46" s="50">
+      <c r="A46" s="49">
         <v>35</v>
       </c>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="C46" s="54"/>
-      <c r="D46" s="51" t="s">
+      <c r="C46" s="53"/>
+      <c r="D46" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="50">
+      <c r="E46" s="49">
         <v>29</v>
       </c>
-      <c r="F46" s="53" t="s">
+      <c r="F46" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="57"/>
-      <c r="H46" s="51" t="s">
+      <c r="G46" s="1"/>
+      <c r="H46" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
-      <c r="A47" s="50">
+      <c r="A47" s="49">
         <v>36</v>
       </c>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="54"/>
-      <c r="D47" s="51" t="s">
+      <c r="C47" s="53"/>
+      <c r="D47" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="E47" s="50">
+      <c r="E47" s="49">
         <v>30</v>
       </c>
-      <c r="F47" s="53" t="s">
+      <c r="F47" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="57"/>
-      <c r="H47" s="51" t="s">
+      <c r="G47" s="1"/>
+      <c r="H47" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
-      <c r="A48" s="50">
+      <c r="A48" s="49">
         <v>37</v>
       </c>
-      <c r="B48" s="51" t="s">
+      <c r="B48" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="54"/>
-      <c r="D48" s="51" t="s">
+      <c r="C48" s="53"/>
+      <c r="D48" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="E48" s="50">
+      <c r="E48" s="49">
         <v>31</v>
       </c>
-      <c r="F48" s="53" t="s">
+      <c r="F48" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="G48" s="57"/>
-      <c r="H48" s="51" t="s">
+      <c r="G48" s="1"/>
+      <c r="H48" s="50" t="s">
         <v>218</v>
       </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18">
-      <c r="A49" s="50">
+      <c r="A49" s="49">
         <v>38</v>
       </c>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="51" t="s">
+      <c r="C49" s="53"/>
+      <c r="D49" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="E49" s="50">
+      <c r="E49" s="49">
         <v>32</v>
       </c>
-      <c r="F49" s="53" t="s">
+      <c r="F49" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="G49" s="57"/>
-      <c r="H49" s="51" t="s">
+      <c r="G49" s="1"/>
+      <c r="H49" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18">
-      <c r="A50" s="50">
+      <c r="A50" s="49">
         <v>39</v>
       </c>
-      <c r="B50" s="51" t="s">
+      <c r="B50" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="51" t="s">
+      <c r="C50" s="53"/>
+      <c r="D50" s="50" t="s">
         <v>221</v>
       </c>
-      <c r="E50" s="50">
+      <c r="E50" s="49">
         <v>33</v>
       </c>
-      <c r="F50" s="53" t="s">
+      <c r="F50" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="57"/>
-      <c r="H50" s="51" t="s">
+      <c r="G50" s="1"/>
+      <c r="H50" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
-      <c r="A51" s="42" t="s">
+      <c r="A51" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="B51" s="43"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
-      <c r="A52" s="42" t="s">
+      <c r="A52" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="43"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5" customFormat="1" s="46">
-      <c r="A54" s="47" t="s">
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5" customFormat="1" s="45">
+      <c r="A54" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="48" t="s">
+      <c r="B54" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="48" t="s">
+      <c r="D54" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="48" t="s">
+      <c r="E54" s="46"/>
+      <c r="F54" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="G54" s="48" t="s">
+      <c r="G54" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="H54" s="48" t="s">
+      <c r="H54" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="I54" s="49"/>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
-      <c r="A55" s="50">
+      <c r="A55" s="49">
         <v>1</v>
       </c>
-      <c r="B55" s="51" t="s">
+      <c r="B55" s="50" t="s">
         <v>225</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="C55" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="51" t="s">
+      <c r="D55" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="53" t="s">
+      <c r="E55" s="49"/>
+      <c r="F55" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="G55" s="55" t="s">
+      <c r="G55" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="H55" s="51" t="s">
+      <c r="H55" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
-      <c r="A56" s="50">
+      <c r="A56" s="49">
         <v>2</v>
       </c>
-      <c r="B56" s="51" t="s">
+      <c r="B56" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="C56" s="55" t="s">
+      <c r="C56" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="51" t="s">
+      <c r="D56" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="E56" s="50"/>
-      <c r="F56" s="53" t="s">
+      <c r="E56" s="49"/>
+      <c r="F56" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="G56" s="55" t="s">
+      <c r="G56" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="H56" s="51" t="s">
+      <c r="H56" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
-      <c r="A57" s="50">
+      <c r="A57" s="49">
         <v>3</v>
       </c>
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="C57" s="55" t="s">
+      <c r="C57" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="D57" s="51" t="s">
+      <c r="D57" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="E57" s="50"/>
-      <c r="F57" s="53" t="s">
+      <c r="E57" s="49"/>
+      <c r="F57" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="G57" s="55" t="s">
+      <c r="G57" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="H57" s="51" t="s">
+      <c r="H57" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
-      <c r="A58" s="50">
+      <c r="A58" s="49">
         <v>4</v>
       </c>
-      <c r="B58" s="51" t="s">
+      <c r="B58" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="55" t="s">
+      <c r="C58" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="D58" s="51" t="s">
+      <c r="D58" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="E58" s="50"/>
-      <c r="F58" s="53" t="s">
+      <c r="E58" s="49"/>
+      <c r="F58" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="G58" s="55" t="s">
+      <c r="G58" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="H58" s="51" t="s">
+      <c r="H58" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
-      <c r="A59" s="50">
+      <c r="A59" s="49">
         <v>5</v>
       </c>
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="55" t="s">
+      <c r="C59" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="D59" s="51" t="s">
+      <c r="D59" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="53" t="s">
+      <c r="E59" s="49"/>
+      <c r="F59" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="G59" s="55" t="s">
+      <c r="G59" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="H59" s="51" t="s">
+      <c r="H59" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
-      <c r="A60" s="50">
+      <c r="A60" s="49">
         <v>6</v>
       </c>
-      <c r="B60" s="51" t="s">
+      <c r="B60" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="C60" s="55" t="s">
+      <c r="C60" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="D60" s="51" t="s">
+      <c r="D60" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="E60" s="50"/>
-      <c r="F60" s="53" t="s">
+      <c r="E60" s="49"/>
+      <c r="F60" s="52" t="s">
         <v>247</v>
       </c>
-      <c r="G60" s="55" t="s">
+      <c r="G60" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H60" s="51" t="s">
+      <c r="H60" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
-      <c r="A61" s="50">
+      <c r="A61" s="49">
         <v>7</v>
       </c>
-      <c r="B61" s="51" t="s">
+      <c r="B61" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="C61" s="55" t="s">
+      <c r="C61" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="51" t="s">
+      <c r="D61" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="E61" s="50"/>
-      <c r="F61" s="53" t="s">
+      <c r="E61" s="49"/>
+      <c r="F61" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="G61" s="55" t="s">
+      <c r="G61" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="H61" s="51" t="s">
+      <c r="H61" s="50" t="s">
         <v>252</v>
       </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
-      <c r="A62" s="50">
+      <c r="A62" s="49">
         <v>8</v>
       </c>
-      <c r="B62" s="51" t="s">
+      <c r="B62" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="C62" s="55" t="s">
+      <c r="C62" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="51" t="s">
+      <c r="D62" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="50"/>
-      <c r="F62" s="53" t="s">
+      <c r="E62" s="49"/>
+      <c r="F62" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="G62" s="55" t="s">
+      <c r="G62" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="H62" s="51" t="s">
+      <c r="H62" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
-      <c r="A63" s="50">
+      <c r="A63" s="49">
         <v>9</v>
       </c>
-      <c r="B63" s="51" t="s">
+      <c r="B63" s="50" t="s">
         <v>257</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="C63" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="51" t="s">
+      <c r="D63" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="E63" s="50"/>
-      <c r="F63" s="53" t="s">
+      <c r="E63" s="49"/>
+      <c r="F63" s="52" t="s">
         <v>259</v>
       </c>
-      <c r="G63" s="55" t="s">
+      <c r="G63" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="H63" s="51" t="s">
+      <c r="H63" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
-      <c r="A64" s="50">
+      <c r="A64" s="49">
         <v>10</v>
       </c>
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="C64" s="55" t="s">
+      <c r="C64" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D64" s="51" t="s">
+      <c r="D64" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="E64" s="50"/>
-      <c r="F64" s="53" t="s">
+      <c r="E64" s="49"/>
+      <c r="F64" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="G64" s="55" t="s">
+      <c r="G64" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="H64" s="51" t="s">
+      <c r="H64" s="50" t="s">
         <v>264</v>
       </c>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
-      <c r="A65" s="50">
+      <c r="A65" s="49">
         <v>11</v>
       </c>
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C65" s="55" t="s">
+      <c r="C65" s="54" t="s">
         <v>148</v>
       </c>
-      <c r="D65" s="51" t="s">
+      <c r="D65" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="E65" s="50"/>
-      <c r="F65" s="53" t="s">
+      <c r="E65" s="49"/>
+      <c r="F65" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="G65" s="55" t="s">
+      <c r="G65" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H65" s="51" t="s">
+      <c r="H65" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
-      <c r="A66" s="50">
+      <c r="A66" s="49">
         <v>12</v>
       </c>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="C66" s="55" t="s">
+      <c r="C66" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="D66" s="51" t="s">
+      <c r="D66" s="50" t="s">
         <v>271</v>
       </c>
-      <c r="E66" s="50"/>
-      <c r="F66" s="53" t="s">
+      <c r="E66" s="49"/>
+      <c r="F66" s="52" t="s">
         <v>272</v>
       </c>
-      <c r="G66" s="55" t="s">
+      <c r="G66" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="H66" s="51" t="s">
+      <c r="H66" s="50" t="s">
         <v>273</v>
       </c>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
-      <c r="A67" s="50">
+      <c r="A67" s="49">
         <v>13</v>
       </c>
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="50" t="s">
         <v>274</v>
       </c>
-      <c r="C67" s="55" t="s">
+      <c r="C67" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D67" s="51" t="s">
+      <c r="D67" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="E67" s="50"/>
-      <c r="F67" s="53" t="s">
+      <c r="E67" s="49"/>
+      <c r="F67" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="G67" s="55" t="s">
+      <c r="G67" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="51" t="s">
+      <c r="H67" s="50" t="s">
         <v>277</v>
       </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
-      <c r="A68" s="50">
+      <c r="A68" s="49">
         <v>14</v>
       </c>
-      <c r="B68" s="51" t="s">
+      <c r="B68" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="C68" s="54" t="s">
+      <c r="C68" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="D68" s="51" t="s">
+      <c r="D68" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="E68" s="50"/>
-      <c r="F68" s="53" t="s">
+      <c r="E68" s="49"/>
+      <c r="F68" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="G68" s="55" t="s">
+      <c r="G68" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="H68" s="51" t="s">
+      <c r="H68" s="50" t="s">
         <v>282</v>
       </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18">
-      <c r="A69" s="50">
+      <c r="A69" s="49">
         <v>15</v>
       </c>
-      <c r="B69" s="51" t="s">
+      <c r="B69" s="50" t="s">
         <v>283</v>
       </c>
-      <c r="C69" s="55" t="s">
+      <c r="C69" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="D69" s="51" t="s">
+      <c r="D69" s="50" t="s">
         <v>284</v>
       </c>
-      <c r="E69" s="50"/>
-      <c r="F69" s="53" t="s">
+      <c r="E69" s="49"/>
+      <c r="F69" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="G69" s="54" t="s">
+      <c r="G69" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="H69" s="51" t="s">
+      <c r="H69" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18">
-      <c r="A70" s="50">
+      <c r="A70" s="49">
         <v>16</v>
       </c>
-      <c r="B70" s="51" t="s">
+      <c r="B70" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="D70" s="51" t="s">
+      <c r="D70" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="E70" s="50"/>
-      <c r="F70" s="53" t="s">
+      <c r="E70" s="49"/>
+      <c r="F70" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="G70" s="57"/>
-      <c r="H70" s="51" t="s">
+      <c r="G70" s="1"/>
+      <c r="H70" s="50" t="s">
         <v>291</v>
       </c>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3419,17 +3407,17 @@
   <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="39" width="13.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="39" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="39" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="39" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="39" width="11.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="39" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="39" width="13.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="39" width="27.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="37" width="13.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="37" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="37" width="10.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="37" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="37" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="37" width="13.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="37" width="27.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
@@ -3763,7 +3751,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="14"/>
       <c r="G18" s="12"/>
-      <c r="H18" s="19"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="2"/>
@@ -3795,16 +3783,16 @@
       <c r="K20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="20"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="22"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21"/>
       <c r="G21" s="12"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
       <c r="K21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -4101,7 +4089,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="19"/>
+      <c r="H44" s="17"/>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
       <c r="K44" s="2"/>
@@ -4133,55 +4121,55 @@
       <c r="K46" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="20"/>
+      <c r="A47" s="19"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
       <c r="G47" s="12"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
       <c r="K47" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="25"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="21"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="12"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
       <c r="K48" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="29"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="21"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="20"/>
       <c r="G49" s="12"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
       <c r="K49" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="31"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="21"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="12"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
       <c r="K50" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -4191,7 +4179,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="33"/>
+      <c r="G51" s="32"/>
       <c r="H51" s="5"/>
       <c r="I51" s="17"/>
       <c r="J51" s="17"/>
@@ -4204,7 +4192,7 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="33"/>
+      <c r="G52" s="32"/>
       <c r="H52" s="5"/>
       <c r="I52" s="17"/>
       <c r="J52" s="17"/>
@@ -4217,7 +4205,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="33"/>
+      <c r="G53" s="32"/>
       <c r="H53" s="5"/>
       <c r="I53" s="17"/>
       <c r="J53" s="17"/>
@@ -4227,8 +4215,8 @@
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4374,7 +4362,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="12"/>
-      <c r="H65" s="19"/>
+      <c r="H65" s="17"/>
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
       <c r="K65" s="2"/>
@@ -4452,7 +4440,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="12"/>
-      <c r="H71" s="19"/>
+      <c r="H71" s="17"/>
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
       <c r="K71" s="2"/>
@@ -4487,8 +4475,8 @@
       <c r="A74" s="11"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
       <c r="F74" s="8"/>
       <c r="G74" s="12"/>
       <c r="H74" s="5"/>
@@ -4569,33 +4557,33 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="12"/>
-      <c r="H80" s="19"/>
+      <c r="H80" s="17"/>
       <c r="I80" s="13"/>
       <c r="J80" s="13"/>
       <c r="K80" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="35"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="36"/>
+      <c r="A81" s="34"/>
+      <c r="B81" s="35"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="35"/>
       <c r="H81" s="2"/>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="35"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="36"/>
-      <c r="H82" s="38"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="35"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="10"/>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
